--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,77 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/.julia/dev/JPEtools/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957E4354-791A-4942-ABF7-9C88724FEAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
-  <si>
-    <t>Data Preparation Program</t>
-  </si>
-  <si>
-    <t>Dataset created</t>
-  </si>
-  <si>
-    <t>Reproduced?</t>
-  </si>
-  <si>
-    <t>Figure/Table #</t>
-  </si>
-  <si>
-    <t>Program</t>
-  </si>
-  <si>
-    <t>Line Number</t>
-  </si>
-  <si>
-    <t>In-text numbers</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,30 +54,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -433,75 +456,1715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M71"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col width="23.5" customWidth="1" min="1" max="1"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="11.5" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="13.5" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="7.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="11.5" bestFit="1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data Preparation Program</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset created</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Reproduced?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Figure/Table #</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Line Number</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Reproduced?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>In-text numbers</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Line Number</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Reproduced?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>import_boardex_na.do</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>wrds_boardex_na.dta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>l.723</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>57 colluding pairs (pp. 15, 23)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>l.636-676</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>import_boardex_na.do</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>wrds_boardex_na_permco.dta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Table 2 (main regressions)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>l.1292</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>845 non-colluding pairs (p. 15)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>l.636-676</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>compare_boardex_wrds.do</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>bex_cs_match.dta / bex_cs_match.csv</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Figure 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>l.987</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.6% rate of collusion among all firm pair-years (p. 17)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>l.754</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>clean_compustat.do</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>clean_compustat.dta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Table 3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>l.1325</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.158 std dev of common leadership (p. 19)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>l.777</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>boardex_network_data_pull_replication.R</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NA - Company Network - Augmented - subset 1990.csv</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Figure A1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>l.1564</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.167 std dev of labor market overlap (p. 19)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>l.779</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>boardex_network_data_pull_replication.R</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NA - Company Network - Augmented.csv</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Figure A2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>l.1466</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.434 std dev of common ownership (p. 19)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>l.781</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BoardEx_FamilyID_trackable_2025.csv</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Figure A3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>l.987</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>47 firm pairs that experience common leadership during sample period (p. 23)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>l.636-676</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LinkedIn_FamilyID_trackable_2025.csv</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Figure A4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>l.987</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>company_network_sample_2025.csv</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Figure A5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>l.987</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>publicFirms_Skeleton.csv</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Table 2 (public firms summary stats)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>public_firms_sumstats.do</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>l.311</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1_Companyid_CUSIP_Crosswalk.do</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>companyid_cusip_crosswalk.dta</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Table A2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>l.1432</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2_Get_Kappas_for_BoardEx-checkpoint.py</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yearly_kappas_2000_2017.parquet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Table B1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>l.1352</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2_Get_Kappas_for_BoardEx-checkpoint.py</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Annual Firmpair Kappas for BoardEx 2000-2017.dta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Table B2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>l.1432</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>panel_connections_by_row_company_network_NA_2025.csv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Table C1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TC1_Panel_leaders_stats.do</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>l.76</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>panel_connections_by_row_family_network_NA_2025.csv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Table C2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TC2_Sample_pair_and_firm_balance_tables.do</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>l.43, 51, 80, 109</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_NA_2025.csv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_family_network_NA_2025.csv</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_insample_balanced_2025.csv</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_replication.R</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_family_network_insample_balanced_2025.csv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_AllSrVpsIN_replication.R</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_NA_2025_AllSrVpsIN.csv</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_AllSrVpsIN_replication.R</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_insample_balanced_2025_AllSrVpsIN.csv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_AllSrVpsOUT_replication.R</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_NA_2025_AllSrVpsOUT.csv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_AllSrVpsOUT_replication.R</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_insample_balanced_2025_AllSrVpsOUT.csv</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_CSuitSubset_replication.R</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_NA_2025_CSuitSubset.csv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>boardex_connections_construct_v5_CSuitSubset_replication.R</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>panel_connections_sumcount_by_company_pairs_company_network_insample_balanced_2025_CSuitSubset.csv</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>individual_counts_v3_replication.R</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>firm_level_counts_preaggregation.csv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>individual_counts_v3_replication.R</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>firm_level_counts.csv</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Leader_Panel.R</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Panel_Leaders.csv</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Create_regression_sample_2025_bexcompanyid_familyid.do</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>regression_sample_2025_bexcompanyid_familyid.csv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Create_Sample_Leaders.do</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sample_Leaders.csv</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Create_Sample_Common_Leaders.do</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sample_Common_Leaders.csv</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>linkedin_raw.csv (synthetic)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>chatgpt jobclassification/raw/0.csv – 49.csv (50 files)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>chatgpt jobclassification/processed/0.xlsx – 30.xlsx (31 files)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>job_categories_gpt.csv</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>cosine distances/out_sample/[company].csv (per-firm files)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cosine distances/[company].csv (per-firm files)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>deduplicating names/checkpoint/checkpoint_1.csv – checkpoint_59.csv (59 files)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>deduplicating names/checkpoint/names_checkpoint_all.csv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>employment chunks/employment_1.rds</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>flows chunks/flows_1.rds</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>temp files/employment_annual.csv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>temp files/flows_annual.csv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>deduplication_directory_2025.csv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>emp_titles_dedup.csv</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>[LinkedIn processing scripts]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>flows_annual.csv</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>connection_agreement_regdata_treatedfamilies_finalregsample_2025.csv</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>connection_agreement_crosstab.csv</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>table_agreement_counts.txt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>table_agreement_counts_family_level.txt</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sumstats_alt_leader_defns.txt</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>public_firms_sumstats.do</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cleaned Data for FirmPair SumStats_V2.dta</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>public_firms_sumstats.do</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cleaned Data for Firm SumStats_V2.dta</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>public_firms_sumstats.do</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>sumstat_public.tex</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>reg_table_agreement_connection_dd_incctrls.tex</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>reg_dd_pairfe_shortwindow_nrw.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>reg_table_agreement_connection_dd_othersamps.tex</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>common_lead_onset_share.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>reg_dd_pairfe_obscount.pdf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>reg_dd_knowndate_pairfe_shortwindow_nrw.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>reg_dd_agpair_pairfe_shortwindow_nrw.pdf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>reg_dd_linkedpair_pairfe_shortwindow_nrw.pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>reg_table_agreement_connection_dd_brdtype.tex</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>reg_table_agreement_connection_dd_leaddefns.tex</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>collusion_connections_regs_v7_replication.R</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>reg_table_agreement_connection_dd_CSuitSubset_brdtype.tex</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC1_Panel_leaders_stats.do</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>panel_leaders_stats_ned_new_l_by_new_cl_notredundant_wide.csv</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC2_Sample_pair_and_firm_balance_tables.do</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>pair_regs_everagreement.csv</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC2_Sample_pair_and_firm_balance_tables.do</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>pair_regs_everconcurrentconnection.csv</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC2_Sample_pair_and_firm_balance_tables.do</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>pair_stats_everagreement.csv</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC2_Sample_pair_and_firm_balance_tables.do</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>pair_stats_everconcurrentconnection.csv</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>